--- a/supplementary_tables/Supplementary_Tables.xlsx
+++ b/supplementary_tables/Supplementary_Tables.xlsx
@@ -135,7 +135,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Strict allele-compatible X→SBP edges (PRIMARY) vs the position-only set they replace</t>
+          <t>Strict allele-compatible X→SBP primary analysis with position-only sensitivity comparison</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <col width="13.5" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="31.2" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Table S6 | Cross-ancestry comparison of every shared edge between European and East Asian (Biobank Japan) networks: effect sizes, P-values, direction concordance and joint significance.</t>
@@ -4015,7 +4015,7 @@
     <col width="13.5" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="31.2" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Table S7 | East Asian MR network, Biobank Japan (BBJ). IVW primary estimate with weighted-median and MR-Egger sensitivity and Steiger direction.</t>
@@ -10195,7 +10195,7 @@
     <col width="13.5" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="31.2" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Table S7b | Inverse-variance meta-analysis of the two East Asian hospital cohorts (BBJ + TPMI), fixed- and random-effects. Fixed-vs-random divergence is reported because high-heterogeneity edges are borderline at Bonferroni (e.g. T2D→BMI).</t>
@@ -11579,7 +11579,7 @@
     <col width="13.5" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="31.2" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Table S8 | Population-vs-hospital triangulation of the diabetes→adiposity (→BMI) edge. Within the population-based KoGES cohort, DM→BMI/WAIST (population) is compared with the hospital BBJ/TPMI estimates; the forward BMI→DM positive control is intact.</t>
@@ -11858,7 +11858,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="51.6" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>DM→BMI IVW point estimate (−0.043) matches the hospital TPMI edge (−0.046): the edge does not vanish in a population cohort, so it is not a demonstrable ascertainment artifact; a causal effect is not established (IVW-random null, balanced pleiotropy). Robust suite: pleiotropy-robust estimators (weighted median −0.090, weighted mode −0.102, penalised weighted median, radial IVW) stay negative, while the conservative two-cohort Hartung–Knapp meta-analysis is non-significant (95% CI [−0.40, +0.26], P = 0.22; k = 2, I² = 0.76). The forward BMI→DM positive control is intact.</t>
@@ -11895,7 +11895,7 @@
     <col width="13.5" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="56.4" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Table S9 | Atherogenic-axis multivariable MR. ApoB retains a direct CAD effect representing the atherogenic lipoprotein axis; ApoB and LDL are too collinear to separate (conditional F collapses when co-modelled), so the claim is axis-level. The full-instrument-density models are included in the same sheet: the HDL→CAD direct effect attenuates by about half at full density but a residual survives, which is why HDL non-causality is not declared from MVMR alone.</t>
@@ -12769,7 +12769,7 @@
     <col width="13.5" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="43.8" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Table S10 | Cross-ancestry scale standardisation. Effect sizes on native and per-SD scales; only SBP required rescaling (EUR per-mmHg → per-SD, SD = 19.3 mmHg), computed from the full-precision IVW estimate rather than the rounded native value shown. HbA1c and eGFR were flagged non-comparable rather than rescaled.</t>
@@ -16940,7 +16940,7 @@
     <col width="13.5" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="31.2" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Table S11 | Liability-scale Steiger directionality (get_r_from_lor) for headline edges. HF→CAD is decisively wrong-direction (variance explained in CAD exceeds that in HF liability).</t>
@@ -17726,7 +17726,7 @@
     <col width="13.5" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="69" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Table S11b | MR-PRESSO across EVERY Bonferroni-significant edge (tiered: full global, outlier-corrected and distortion battery for edges with at most 130 harmonised instruments; global test alone above that, since the outlier and distortion tests scale with resampling count times squared instrument count). The global test is significant for every edge, which is expected at these instrument counts and indicates heterogeneity rather than bias; the interpretable quantity is the distortion test. Only HF→CAD is materially distorted by outlier correction (raw 0.807 → corrected 0.509; 13 outliers; distortion P &lt; 0.001).</t>
@@ -19939,7 +19939,7 @@
       </c>
       <c r="K61" s="7" t="n"/>
     </row>
-    <row r="63">
+    <row r="63" ht="28.8" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
         <is>
           <t>Tier column records which edges received the full battery. Five edges are distortion-significant: HF→CAD, HF→Stroke, T2D→HbA1c, T2D→HDL and T2D→SBP; HF→CAD is the reverse edge the manuscript already flags.</t>
@@ -19983,7 +19983,7 @@
     <col width="13.5" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="43.8" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Table S12 | UK-Biobank-free outcome-side sensitivity analysis. Headline European edges re-estimated against UK-Biobank-free outcome GWAS (CARDIoGRAM CAD, HERMES-noUKB HF, Mahajan-noUKB T2D, MEGASTROKE, CKDGen) and the fully independent FinnGen R12. All 13 headline forward edges retain sign and Bonferroni significance at 0.05/132; the staging order rebuilt on these outcomes stays beyond chance (concordance 0.960, exact P = 7.6 × 10⁻⁴ main; 0.913, exact P = 7.6 × 10⁻⁴ FinnGen). Four Stroke-as-exposure directions have no UK-Biobank-free counterpart and retain their primary estimates. This removes outcome-side overlap only — the BMI and SBP exposure GWAS still include UK Biobank.</t>
@@ -25018,7 +25018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" ht="28.8" customHeight="1">
       <c r="A85" s="8" t="inlineStr">
         <is>
           <t>Feedback edges CAD→T2D and HF→T2D attenuate on the outcome-overlap-removed Mahajan T2D, but independent FinnGen keeps CAD→T2D strongly (P ≈ 9 × 10⁻⁹); HF→T2D is the one fragile edge. Steiger for FinnGen/MEGASTROKE/CKDGen/Mahajan uses a constant N (affects Steiger direction only, not β/P).</t>
@@ -25053,7 +25053,7 @@
     <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="43.8" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Table S1 | GWAS data sources. Exposure and outcome summary statistics used to construct the European and East Asian CKM networks and the UK-Biobank-free sensitivity analysis. Sample sizes are shown where unambiguous; full details are in the cited reference. '—' indicates not separately tabulated here (see reference/accession).</t>
@@ -26194,7 +26194,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="28.8" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>TPMI and KoGES are available under controlled access. Reference keys map to the reference list in the manuscript References section.</t>
@@ -26237,7 +26237,7 @@
     <col width="13.5" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="31.2" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Table S13 | Binary chronic-kidney-disease (CKD) node (Wuttke 2019, GCST008065), a kidney-damage endpoint distinct from the quantitative eGFR node. Risk-factor→CKD edges fall in graded tiers: robust (BMI, SBP, HF: IVW and weighted median significant, clean Egger intercept) versus pleiotropy-suspect (HDL, TG: weighted median null, significant Egger intercept). CKD→cardiovascular edges are null but underpowered (~24 instruments).</t>
@@ -27054,10 +27054,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="17.4" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>This node is distinct from the Zheng-replication SBP→CKD / BMI→CKD comparison shown for the ancestry-divergence analysis (Fig 5a), which uses a separate CKD analysis.</t>
+          <t>This node is distinct from the Zheng-replication SBP→CKD / BMI→CKD comparison shown for the ancestry-divergence analysis (Supplementary Figure S6a), which uses a separate CKD analysis.</t>
         </is>
       </c>
     </row>
@@ -27086,7 +27086,7 @@
     <col width="46" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="106.8" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Table S14 | Sample-overlap structure. Two-sample MR assumes little exposure–outcome sample overlap; overlap biases estimates toward the confounded observational association. In Europeans overlap arises mainly through shared UK Biobank participants; the outcome-side UK-Biobank-free sensitivity analysis (Table S12) removes it on the outcome side, and the exposure-side UKB overlap (BMI, SBP) is disclosed as a limitation. In East Asians the within-cohort networks are one-sample; the zero-overlap BBJ→TPMI design (Table S19) provides the clean check.</t>
@@ -27521,7 +27521,7 @@
     <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="106.8" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Table S15 | Cross-ancestry scale dictionary. Per-trait exposure scale on each ancestry side and whether raw magnitudes are directly comparable. Magnitude or ratio comparisons are made only for the 'comparable' rows on a common scale; SBP is compared only after converting the European per-mmHg estimate to per-SD (SD = 19.3 mmHg); HbA1c and eGFR are read on sign concordance only, never magnitude.</t>
@@ -27739,7 +27739,7 @@
     <col width="13.5" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="43.8" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Table S16 | Coronary-artery-calcium (CAC) node (Kavousi 2023, GCST90278456; European stratum, 26,909), the guideline-named subclinical stage-3 marker. Stage-1/2→CAC edges are robust (hundreds of instruments); the stage-3→4 bridge (CAC→CAD) rests on only 5–6 instruments and is pleiotropy-prone. Adding this all-forward tier raises the staging concordance from 0.926 to 0.941 (exact permutation P = 1.2 × 10⁻⁴); the informative result is that no backward CAC edge appeared among the directions tested — nine CAC-to-risk-factor directions were not estimated, so a backward edge could not have been detected.</t>
@@ -28668,7 +28668,7 @@
         <v>6.45037169675063e-17</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="17.4" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>The 9p21 lead rs4977575 is dropped as an ambiguous palindrome, leaving CAC→CAD on 5 instruments; dropping this thin edge leaves concordance 0.939.</t>
@@ -28707,10 +28707,10 @@
     <col width="13.5" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="94.2" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table S17 | All-aetiology heart-failure subtypes (Enzan 2025, PMID 41184235; HFpEF GCST90654629, HFrEF GCST90654628). These replace an earlier non-ischaemic panel, which was circular by construction: coronary disease is null against non-ischaemic HF by case definition. With ischaemic cases retained, CAD reaches both subtypes (HFpEF P = 6e-13; HFrEF P = 6e-42), adiposity reaches both, and T2D reaches HFrEF but not HFpEF (P = 0.55). Between-subtype differences are TESTED, not inferred from significance patterns: CAD differs strongly (HFrEF &gt; HFpEF, P = 2.2e-09, surviving Bonferroni over 8 exposures), T2D only nominally (P = 7.5e-03), and BMI shows no detected difference (P = 0.74) — an absence of evidence, not equivalence. These outcomes are cross-ancestry (EUR+EAS), so predominantly European instruments act on a ~42%-East-Asian sample, which limits interpretation of magnitude; edges are read on direction, not magnitude, and the EAS component overlaps the Biobank Japan HF outcome used elsewhere.</t>
+          <t>Table S17 | All-aetiology heart-failure subtypes (Enzan 2025, PMID 41184235; HFpEF GCST90654629, HFrEF GCST90654628). All-aetiology subtype outcomes are used because definitions excluding ischaemic cases condition directly on CAD, which would make coronary disease null against non-ischaemic HF by case definition. With ischaemic cases retained, CAD reaches both subtypes (HFpEF P = 6e-13; HFrEF P = 6e-42), adiposity reaches both, and T2D reaches HFrEF but not HFpEF (P = 0.55). Between-subtype differences are TESTED, not inferred from significance patterns: CAD differs strongly (HFrEF &gt; HFpEF, P = 2.2e-09, surviving Bonferroni over 8 exposures), T2D only nominally (P = 7.5e-03), and BMI shows no detected difference (P = 0.74) — an absence of evidence, not equivalence. These outcomes are cross-ancestry (EUR+EAS), so predominantly European instruments act on a ~42%-East-Asian sample, which limits interpretation of magnitude; edges are read on direction, not magnitude, and the EAS component overlaps the Biobank Japan HF outcome used elsewhere.</t>
         </is>
       </c>
     </row>
@@ -29448,7 +29448,7 @@
         <v>5.80669451833963e-29</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="40.2" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>T2D→HFrEF is IVW-positive but attenuates under weighted-median (~0.046) and MR-Egger (~0.022); report the direction and range, not a firm magnitude. Full between-subtype heterogeneity tests across five assumed correlations are given in the deposited hf_subtype_heterogeneity.csv; rho = 0 is the conservative column because the shared control set induces positive correlation.</t>
@@ -29487,7 +29487,7 @@
     <col width="13.5" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="43.8" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Table S18 | Adiposity distribution independent of overall mass (WHRadjBMI; Pulit 2019, 694,649 European, combined-sex). Central fat distribution is consistent with a causal effect on CAD and T2D but not on heart failure: no WHRadjBMI–HF association was detected. Because the exposure is conditioned on BMI and the estimates are heterogeneous, this does not establish whether overall mass or fat distribution carries the risk. Steiger filtering was not applied to these edges.</t>
@@ -29808,7 +29808,7 @@
         <v>7.87262237465376e-193</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="28.8" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Two caveats: WHRadjBMI is BMI-adjusted (conditioning on a heritable covariate can induce collider bias, so the null-to-inverse HF association is not read as protective); and WHRadjBMI shares UK Biobank with the CAD, HF and T2D outcomes, so direction is firmer than magnitude.</t>
@@ -29847,7 +29847,7 @@
     <col width="13.5" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="43.8" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Table S19 | Zero-overlap cross-cohort East Asian MR: Biobank Japan instruments against Taiwan (TPMI) outcomes, sharing no participants (a clean two-sample design addressing within-cohort overlap). The core cascade (BMI→CAD/HF, LDL/TC→CAD, HbA1c→T2D, SBP→stroke) replicates with no overlap; BMI→T2D does not (null cross-cohort and within-BBJ, significant only within TPMI), a discrepancy compatible with overlap and/or cohort differences rather than attributable to either alone.</t>
@@ -31806,7 +31806,7 @@
         <v>1.96368564577841e-15</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="40.2" customHeight="1">
       <c r="A49" s="8" t="inlineStr">
         <is>
           <t>Liftover hg19→hg38; allele-compatibility checked at extraction. SBP→CAD/HF attenuate to null cross-cohort (SBP→stroke survives), consistent with reduced power of the smaller blood-pressure instrument set. The CAD→CAD row is not a causal self-edge: it applies the Biobank Japan coronary instruments to the independent Taiwan coronary outcome and is reported as instrument / positive-control validation of the cross-cohort design (β = +0.388, *P* = 1.9 × 10⁻²⁹).</t>
@@ -31843,7 +31843,7 @@
     <col width="13.5" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="69" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Table S20 | Steiger direction margins for every edge in the staging graph. The margin is r²exposure / r²outcome at the base prevalence; Steiger calls the direction correct when it exceeds 1, so the margin — not a prevalence sweep — is what shows whether a direction call is fragile. The smallest margin anywhere in the graph is TG→T2D at 1.92×, and the largest is HbA1c→Stroke at 135×. A 40-fold prevalence range moves the summed r² by about 3%, far less than any of these margins, so the direction calls are not conditional on the assumed prevalence.</t>
@@ -33330,7 +33330,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="28.8" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
           <t>Margin low/high are the endpoints across the prevalence grid. This analysis is one-sided: it covers edges the quantitative Steiger gate already admitted and cannot recover an edge the gate wrongly rejected.</t>
@@ -33368,10 +33368,10 @@
     <col width="13.5" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="81.59999999999999" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table S21 | Disease- and trait-to-SBP edges re-estimated on strict allele-compatible instruments, which are now the PRIMARY analysis. The SBP outcome statistics are keyed by position with no rsID, so extraction matched on position alone and allele compatibility was enforced only at harmonisation; harmonisation cannot repair a row selected wrongly at extraction. The strict set keeps only allele-matched and strand-flip variants, dropping every strand-ambiguous one. Point estimates move — CAD→SBP goes +1.82 to +1.48 — and exactly one edge changes significance status: HDL→SBP falls below the network Bonferroni threshold, taking the network from 59 to 58 Bonferroni-significant edges and the Steiger-directed graph from 54 to 53. HDL→SBP is intra-stage, so cross-stage concordance is unchanged at 0.926 (25/27).</t>
+          <t>Table S21 | Disease- and trait-to-SBP edges re-estimated on strict allele-compatible instruments, which are the primary analysis. The SBP outcome statistics are keyed by position with no rsID, so extraction matched on position alone and allele compatibility was enforced only at harmonisation; harmonisation cannot repair a row selected wrongly at extraction. The strict set keeps only allele-matched and strand-flip variants, dropping every strand-ambiguous one. Point estimates differ between the two extractions — CAD→SBP is +1.48 on the strict set against +1.82 on the position-only set — and exactly one edge differs in significance status: HDL→SBP sits below the network Bonferroni threshold on the strict set, giving 58 Bonferroni-significant edges and a 53-edge Steiger-directed graph. HDL→SBP is intra-stage, so cross-stage concordance is unchanged at 0.926 (25/27).</t>
         </is>
       </c>
     </row>
@@ -33905,10 +33905,10 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="40.2" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>The position-only columns are retained for transparency; they are the set the primary analysis replaces, not an alternative analysis. At the genome-wide-strict bar CAD→SBP no longer clears 5e-8 (P = 1.11e-07), so that robustness variant now reads 1.000 (19/19) — higher than the primary only because the discordant edge fell below a threshold.</t>
+          <t>Position-only estimates are retained as a transparency sensitivity comparator, not as an alternative primary analysis. At the genome-wide-strict bar CAD→SBP does not clear 5e-8 (P = 1.11e-07), so that robustness variant reads 1.000 (19/19) — higher than the primary only because the discordant edge falls below a threshold.</t>
         </is>
       </c>
     </row>
@@ -33941,10 +33941,10 @@
     <col width="13.5" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="56.4" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table S22 | Mixing diagnostics for the degree-preserving rewiring null, the analysis that bounds the staging conclusion. The earlier implementation attempted three times the edge count in double-edge swaps per replicate, skipped invalid proposals without retrying, and reported no realised-swap or turnover statistic. Chain length here is measured in SUCCESSFUL swaps per edge, and the null P is reported at 10×, 25×, 50× and 100× across three independent seeds, alongside acceptance rate and edge turnover, so that the conclusion rests on a measured chain.</t>
+          <t>Table S22 | Mixing diagnostics for the degree-preserving rewiring null, the analysis that bounds the staging conclusion. Chain length is measured in SUCCESSFUL double-edge swaps per edge — invalid proposals are retried rather than skipped, so the realised chain is the reported one — and the null P is reported at 10×, 25×, 50× and 100× across three independent seeds, alongside acceptance rate and edge turnover, so that the conclusion rests on a measured chain.</t>
         </is>
       </c>
     </row>
@@ -34343,7 +34343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="28.8" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Turnover is the fraction of the observed graph's edges no longer present after rewiring; it shows the chain leaves the neighbourhood of the observed graph rather than resampling it.</t>
@@ -34387,7 +34387,7 @@
     <col width="13.5" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="31.2" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Table S2 | Full European-ancestry bidirectional MR network: all 132 directed exposure–outcome edges. IVW is the primary estimate; MR-Egger, weighted median, Egger intercept, Cochran Q, the derived heterogeneity I² = (Q − df)/Q, and liability-scale Steiger direction are reported for each edge. Effect sizes: per-SD (continuous exposure) or per-log-OR (binary).</t>
@@ -42269,7 +42269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" ht="28.8" customHeight="1">
       <c r="A136" s="8" t="inlineStr">
         <is>
           <t>Bonferroni threshold for the network = 0.05/132 = 3.8×10⁻⁴. Steiger direction for the network table uses the quantitative-trait approximation; the liability-scale recomputation for the edges carrying directional claims is Table S11. I², heterogeneity index; WM, weighted median.</t>
@@ -42306,7 +42306,7 @@
     <col width="13.5" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="43.8" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Table S3 | Multivariable MR adjudicating cascade versus common-driver mechanism. Each disease outcome is conditioned jointly on its candidate upstream exposures; the direct effect is the MVMR-IVW estimate and the total effect is the univariable estimate. Conditional F &gt; 12 indicates adequate conditional instrument strength.</t>
@@ -42821,7 +42821,7 @@
         <v>43.241760013315</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="28.8" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Key contrasts: BMI retains a direct effect on CAD and HF; no CAD-independent T2D→HF effect is detected, and the mediated component is substantial but imprecise and covariance-dependent, so no single proportion is reported (Table S3/mediation); LDL→stroke collapses.</t>
@@ -42859,7 +42859,7 @@
     <col width="13.5" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="43.8" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Table S3b | Multivariable MR robustness: an orientation-based multivariable Egger regression (variants oriented on the primary exposure, the intercept serving as the directional-pleiotropy test) and Q-minimisation (qhet) direct effects for the same models as Table S3. Direct slopes survive across estimators; the multivariable-Egger intercept is orientation-dependent for the CAD-outcome models (InSIDE bounded, not absent).</t>
@@ -43445,7 +43445,7 @@
     <col width="13.5" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="43.8" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Table S4 | CAUSE analysis of 10 headline edges, separating correlated pleiotropy from causation. A negative Δ-ELPD z (sharing-vs-causal) with P &lt; 0.05 favours the causal model; γ is the causal effect (posterior median, 95% credible interval); q is the proportion of variants showing correlated pleiotropy.</t>
@@ -43919,7 +43919,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="17.4" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>CAD→HF strongly causal; CAD→T2D and HF→T2D causal (reciprocal feedback); T2D→HF and HbA1c→T2D return as sharing.</t>
@@ -43957,7 +43957,7 @@
     <col width="13.5" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="31.2" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Table S4b | CAUSE correlated-marker negative control on confounded-not-causal lipid pairs. CAUSE misclassifies HDL→CAD as causal — a documented failure mode for correlated-marker exposures — so every lipid CAUSE verdict is read alongside multivariable MR (Table S9).</t>
@@ -44146,7 +44146,7 @@
     <col width="13.5" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="43.8" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Table S5 | Falsifiable staging ledger, adjudicated on NATIVE effect-size scales. Each of 15 AHA stage transitions is tested against its reverse edge by comparing the reverse 95% confidence interval, in that edge's own units, with a negligibility bound set for the outcome's scale (log(1.05) = 0.049 log-odds for binary outcomes; 1 mmHg for SBP; 0.05 SD otherwise). Cross-direction power comparisons are avoided because forward and reverse estimands are measured on different scales; a power-based minimum detectable effect and a fixed-bound equivalence statistic are retained in the last two columns for reference only. The bounds are clinical judgements, and Table S5b reports every verdict across a sweep of them.</t>
@@ -45395,7 +45395,7 @@
         <v>0.9999997958669224</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="28.8" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Verdicts: 7 concordant, 4 indeterminate, 2 with a genuine reverse effect (HF→T2D, Stroke→T2D) and 2 pleiotropy-caveated (CAD→SBP index-event; CAD→T2D feedback-with-caveat, matching the independent H5 robust suite). All four reverse effects point into a lower-stage trait as feedback or an index-event effect, not reverse stage progression. BMI→Stroke is flagged borderline: its reverse CI limit (+0.0505) sits 0.0005 from the 0.05 SD bound, so that verdict would flip under trivial re-rounding.</t>
@@ -45429,7 +45429,7 @@
     <col width="13.5" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="81.59999999999999" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Table S5b | Bound sensitivity of the staging ledger. Each transition's verdict under five negligibility-bound scenarios, from very tight (odds ratio 1.01 / 0.5 mmHg / 0.02 SD) to very loose (odds ratio 1.20 / 5 mmHg / 0.20 SD); the PRIMARY column is the rule reported in Table S5. The concordant/indeterminate split is bound-conditional, but the falsification claim is not: under every scenario each reverse effect in the discordant family runs from a stage-4 disease into a stage-2 trait, as feedback or an index-event effect, and none reverses the staging order.</t>
